--- a/data/trans_bre/P1_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
